--- a/stories/arbres/ATOM-JEU.REG.002-05.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léandre est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Léandre tend la main. Papa va rappeler la règle une fois. Il dit : on attend. C'est la règle. Léandre attend. Puis il pose un cube. Papa dit : tu as suivi la règle. Léandre répète : une règle. Papa la rappelle. Léandre la suit.</t>
+          <t>Léandre est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Léandre tend la main. Papa va rappeler la règle une fois. On attend. C'est la règle. Léandre attend. Puis il pose un cube. Tu as suivi la règle. Léandre répète : une règle. Papa la rappelle. Léandre la suit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léandre est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Léandre tend la main. Papa va rappeler la règle une fois.
+narrateur|On attend. C'est la règle.
+narrateur|Léandre attend. Puis il pose un cube.
+papa|Tu as suivi la règle.
+narrateur|Léandre répète : une règle. Papa la rappelle. Léandre la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léandre joue. Que suit-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léandre a suivi la règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range les cubes. Léandre donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-05.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Léandre répète : une règle. Papa la rappelle. Léandre la suit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Léandre joue. Que suit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Léandre a suivi la règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Papa range les cubes. Léandre donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.002-05.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léandre suit la règle des cubes</t>
+          <t>Les cubes d'Aniss sur le tapis bleu</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sur le tapis bleu, Aniss attend, puis pose un cube. Papa rappelle la règle une fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léandre est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Léandre tend la main. Papa va rappeler la règle une fois. On attend. C'est la règle. Léandre attend. Puis il pose un cube. Tu as suivi la règle. Léandre répète : une règle. Papa la rappelle. Léandre la suit.</t>
+          <t>Le tapis bleu sent la laine un peu. Il est épais sous les genoux. Un cube rouge a roulé sous la table. Une caisse en bois dépasse du canapé. Dedans, des cubes rouges, jaunes, verts. Un rayon se pose sur un cube bleu. Le bois de la caisse est un peu rêche. Un coussin a glissé près de la caisse. La vapeur de soupe fait un petit nuage. La soupe sent bon, depuis la cuisine. Un fil de laine dépasse du tapis. Le canapé a un coussin un peu plat. Tu as vu le cube bleu, Aniss ? Oui, papa. Il brille. En ce moment, papa pose la caisse. Les cubes font un petit bruit de bois. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Aniss attend, un cube jaune dans la main. Puis il pose le cube. Le bois fait clic sur le tapis. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Aniss. On attend. Puis on pose un cube. Oui. Une règle simple. Je la rappelle une fois. Aniss attend encore. Puis il pose un cube rouge. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. La soupe sent encore, tout près. Le rayon a bougé sur le tapis. Encore un cube, tout doux ? Oui, papa. Aniss attend. Puis il pose un cube vert. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le coussin reste près de la caisse. Tu as les genoux sur le tapis ? Oui. Il est épais. On attend, puis on pose. Bravo. Aniss prend le cube sous la table. Il le pose dans la caisse, tout doux. Tu as suivi la règle. Une règle. On la rappelle. Puis on pose.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léandre est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Léandre tend la main. Papa va rappeler la règle une fois.
-narrateur|On attend. C'est la règle.
-narrateur|Léandre attend. Puis il pose un cube.
+          <t>narrateur|Le tapis bleu sent la laine un peu.
+narrateur|Il est épais sous les genoux.
+narrateur|Un cube rouge a roulé sous la table.
+narrateur|Une caisse en bois dépasse du canapé.
+narrateur|Dedans, des cubes rouges, jaunes, verts.
+narrateur|Un rayon se pose sur un cube bleu.
+narrateur|Le bois de la caisse est un peu rêche.
+narrateur|Un coussin a glissé près de la caisse.
+narrateur|La vapeur de soupe fait un petit nuage.
+narrateur|La soupe sent bon, depuis la cuisine.
+narrateur|Un fil de laine dépasse du tapis.
+narrateur|Le canapé a un coussin un peu plat.
+papa|Tu as vu le cube bleu, Aniss ?
+enfant-m|Oui, papa. Il brille.
+narrateur|En ce moment, papa pose la caisse.
+narrateur|Les cubes font un petit bruit de bois.
+papa|Une règle. On attend.
+papa|Puis on pose un cube.
+enfant-m|J'ai envie de poser.
+papa|On attend. Je te la rappelle une fois.
+papa|C'est la règle.
+narrateur|Aniss attend, un cube jaune dans la main.
+narrateur|Puis il pose le cube.
+narrateur|Le bois fait clic sur le tapis.
+enfant-m|Clic.
 papa|Tu as suivi la règle.
-narrateur|Léandre répète : une règle. Papa la rappelle. Léandre la suit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu as attendu. Bravo, Aniss.
+enfant-m|On attend. Puis on pose un cube.
+papa|Oui. Une règle simple.
+papa|Je la rappelle une fois.
+narrateur|Aniss attend encore.
+narrateur|Puis il pose un cube rouge.
+papa|Tu as suivi la règle dite.
+papa|Bravo. Tu as fait du bon travail.
+enfant-m|Une règle. On attend.
+papa|Oui. On la rappelle. Tu la suis.
+narrateur|La soupe sent encore, tout près.
+narrateur|Le rayon a bougé sur le tapis.
+papa|Encore un cube, tout doux ?
+enfant-m|Oui, papa.
+narrateur|Aniss attend.
+narrateur|Puis il pose un cube vert.
+papa|Bravo. Tu as attendu.
+enfant-m|J'ai suivi la règle.
+papa|Oui. Une règle. On la rappelle.
+narrateur|Le coussin reste près de la caisse.
+papa|Tu as les genoux sur le tapis ?
+enfant-m|Oui. Il est épais.
+papa|On attend, puis on pose. Bravo.
+narrateur|Aniss prend le cube sous la table.
+narrateur|Il le pose dans la caisse, tout doux.
+papa|Tu as suivi la règle. Une règle.
+enfant-m|On la rappelle. Puis on pose.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léandre joue. Que suit-il ?</t>
+          <t>Aniss joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léandre joue. Que suit-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss joue.
+narrateur|Que suit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léandre a suivi la règle. Papa l'a rappelée.</t>
+          <t>Aniss a suivi la règle. Papa l'a rappelée. Tu as attendu, puis tu as posé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le cube bleu brille encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1731,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léandre a suivi la règle. Papa l'a rappelée.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a suivi la règle.
+narrateur|Papa l'a rappelée.
+papa|Tu as attendu, puis tu as posé ?
+enfant-m|Oui. Une règle.
+papa|Bravo. On la rappelle, et on la suit.
+narrateur|Le cube bleu brille encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range les cubes. Léandre donne la main.</t>
+          <t>On range les cubes ? Oui, papa. Papa range les cubes dans la caisse. Aniss donne la main. On va vers la soupe ? Oui. Elle sent bon. Le tapis bleu reste un peu chaud. Le fil de laine, tu l'as vu ? Oui. Il dépasse. La vapeur de soupe est encore là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1903,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range les cubes. Léandre donne la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|On range les cubes ?
+enfant-m|Oui, papa.
+narrateur|Papa range les cubes dans la caisse.
+narrateur|Aniss donne la main.
+papa|On va vers la soupe ?
+enfant-m|Oui. Elle sent bon.
+narrateur|Le tapis bleu reste un peu chaud.
+papa|Le fil de laine, tu l'as vu ?
+enfant-m|Oui. Il dépasse.
+narrateur|La vapeur de soupe est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1939,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La soupe fume dans les bols. J'ai attendu. Puis j'ai posé. Oui. Tu as suivi la règle. Bravo, Aniss. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2079,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La soupe fume dans les bols.
+enfant-m|J'ai attendu. Puis j'ai posé.
+papa|Oui. Tu as suivi la règle.
+papa|Bravo, Aniss.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-05.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le tapis bleu sent la laine un peu. Il est épais sous les genoux. Un cube rouge a roulé sous la table. Une caisse en bois dépasse du canapé. Dedans, des cubes rouges, jaunes, verts. Un rayon se pose sur un cube bleu. Le bois de la caisse est un peu rêche. Un coussin a glissé près de la caisse. La vapeur de soupe fait un petit nuage. La soupe sent bon, depuis la cuisine. Un fil de laine dépasse du tapis. Le canapé a un coussin un peu plat. Tu as vu le cube bleu, Aniss ? Oui, papa. Il brille. En ce moment, papa pose la caisse. Les cubes font un petit bruit de bois. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Aniss attend, un cube jaune dans la main. Puis il pose le cube. Le bois fait clic sur le tapis. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Aniss. On attend. Puis on pose un cube. Oui. Une règle simple. Je la rappelle une fois. Aniss attend encore. Puis il pose un cube rouge. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. La soupe sent encore, tout près. Le rayon a bougé sur le tapis. Encore un cube, tout doux ? Oui, papa. Aniss attend. Puis il pose un cube vert. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le coussin reste près de la caisse. Tu as les genoux sur le tapis ? Oui. Il est épais. On attend, puis on pose. Bravo. Aniss prend le cube sous la table. Il le pose dans la caisse, tout doux. Tu as suivi la règle. Une règle. On la rappelle. Puis on pose.</t>
+          <t>Le tapis bleu sent la laine un peu. Il est épais sous les genoux. Un cube rouge a roulé sous la table. Une caisse en bois dépasse du canapé. Dedans, des cubes rouges, jaunes, verts. Un rayon se pose sur un cube bleu. Le bois de la caisse est un peu rêche. Un coussin a glissé près de la caisse. La vapeur de soupe fait un petit nuage. La soupe sent bon, depuis la cuisine. Un fil de laine dépasse du tapis. Le canapé a un coussin un peu plat. Tu as vu le cube bleu, Aniss ? Oui, papa. Il brille. En ce moment, papa pose la caisse. Les cubes font un petit bruit de bois. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Aniss attend, un cube jaune dans la main. Puis il pose le cube. Le bois fait clic sur le tapis. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Aniss. On attend. Puis on pose un cube. Oui. Une règle simple. Je la rappelle une fois. Aniss attend encore. Puis il pose un cube rouge. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La soupe sent encore, tout près. Le rayon a bougé sur le tapis. Encore un cube, tout doux ? Oui, papa. Aniss attend. Puis il pose un cube vert. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le coussin reste près de la caisse. Tu as les genoux sur le tapis ? Oui. Il est épais. On attend, puis on pose. Bravo. Aniss prend le cube sous la table. Il le pose dans la caisse, tout doux. Tu as suivi la règle. Une règle. On la rappelle. Puis on pose.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léandre est dans le salon avec papa. Des cubes sont au sol. Papa dit &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; règle. La règle : on attend. Puis on pose un cube. Léandre tend la main. Papa va rappeler la règle une fois. Il dit : on attend. C'est la règle. Léandre attend. Puis il pose un cube. Papa dit : tu as suivi la règle. Léandre répète : une règle. Papa la rappelle. Léandre la suit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le tapis bleu sent la laine un peu. Il est épais sous les genoux. Un cube rouge a roulé sous la table. Une caisse en bois dépasse du canapé. Dedans, des cubes rouges, jaunes, verts. Un rayon se pose sur un cube bleu. Le bois de la caisse est un peu rêche. Un coussin a glissé près de la caisse. La vapeur de soupe fait un petit nuage. La soupe sent bon, depuis la cuisine. Un fil de laine dépasse du tapis. Le canapé a un coussin un peu plat. Tu as vu le cube bleu, Aniss ? Oui, papa. Il brille. En ce moment, papa pose la caisse. Les cubes font un petit bruit de bois. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Aniss attend, un cube jaune dans la main. Puis il pose le cube. Le bois fait clic sur le tapis. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Aniss. On attend. Puis on pose un cube. Oui. Une règle simple. Je la rappelle une fois. Aniss attend encore. Puis il pose un cube rouge. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La soupe sent encore, tout près. Le rayon a bougé sur le tapis. Encore un cube, tout doux ? Oui, papa. Aniss attend. Puis il pose un cube vert. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le coussin reste près de la caisse. Tu as les genoux sur le tapis ? Oui. Il est épais. On attend, puis on pose. Bravo. Aniss prend le cube sous la table. Il le pose dans la caisse, tout doux. Tu as suivi la règle. Une règle. On la rappelle. Puis on pose.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 narrateur|Aniss attend encore.
 narrateur|Puis il pose un cube rouge.
 papa|Tu as suivi la règle dite.
-papa|Bravo. Tu as fait du bon travail.
 enfant-m|Une règle. On attend.
 papa|Oui. On la rappelle. Tu la suis.
 narrateur|La soupe sent encore, tout près.
@@ -1408,7 +1407,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léandre joue. Que suit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1592,7 +1591,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léandre a suivi &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; règle. Papa l'a rappelée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a suivi la règle. Papa l'a rappelée. Tu as attendu, puis tu as posé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le cube bleu brille encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1768,7 +1767,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range les cubes. Léandre donne &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range les cubes ? Oui, papa. Papa range les cubes dans la caisse. Aniss donne la main. On va vers la soupe ? Oui. Elle sent bon. Le tapis bleu reste un peu chaud. Le fil de laine, tu l'as vu ? Oui. Il dépasse. La vapeur de soupe est encore là.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La soupe fume dans les bols. J'ai attendu. Puis j'ai posé. Oui. Tu as suivi la règle. Bravo, Aniss. L'histoire est finie.</t>
+          <t>La soupe fume dans les bols. J'ai attendu. Puis j'ai posé. Oui. Tu as suivi la règle. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe fume dans les bols. J'ai attendu. Puis j'ai posé. Oui. Tu as suivi la règle. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2082,8 +2081,7 @@
           <t>narrateur|La soupe fume dans les bols.
 enfant-m|J'ai attendu. Puis j'ai posé.
 papa|Oui. Tu as suivi la règle.
-papa|Bravo, Aniss.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Aniss.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2147,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-05.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, tapis bleu, caisse en bois, odeur de soupe</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léandre, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-05.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-05.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les cubes d'Aniss sur le tapis bleu</t>
+          <t>La tour sous la pluie</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon, tapis bleu, caisse en bois, odeur de soupe</t>
+          <t>salon de ville, tapis rouge, pluie, soupe</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aniss, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sur le tapis bleu, Aniss attend, puis pose un cube. Papa rappelle la règle une fois.</t>
+          <t>Nino veut une tour de cubes pendant la pluie. Il pose trop tôt, la tour tombe sous le canapé. Ils attendent un peu. Un cube, puis l'autre. La tour sent le sapin, presque aussi haute que le fauteuil.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le tapis bleu sent la laine un peu. Il est épais sous les genoux. Un cube rouge a roulé sous la table. Une caisse en bois dépasse du canapé. Dedans, des cubes rouges, jaunes, verts. Un rayon se pose sur un cube bleu. Le bois de la caisse est un peu rêche. Un coussin a glissé près de la caisse. La vapeur de soupe fait un petit nuage. La soupe sent bon, depuis la cuisine. Un fil de laine dépasse du tapis. Le canapé a un coussin un peu plat. Tu as vu le cube bleu, Aniss ? Oui, papa. Il brille. En ce moment, papa pose la caisse. Les cubes font un petit bruit de bois. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Aniss attend, un cube jaune dans la main. Puis il pose le cube. Le bois fait clic sur le tapis. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Aniss. On attend. Puis on pose un cube. Oui. Une règle simple. Je la rappelle une fois. Aniss attend encore. Puis il pose un cube rouge. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La soupe sent encore, tout près. Le rayon a bougé sur le tapis. Encore un cube, tout doux ? Oui, papa. Aniss attend. Puis il pose un cube vert. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le coussin reste près de la caisse. Tu as les genoux sur le tapis ? Oui. Il est épais. On attend, puis on pose. Bravo. Aniss prend le cube sous la table. Il le pose dans la caisse, tout doux. Tu as suivi la règle. Une règle. On la rappelle. Puis on pose.</t>
+          <t>La pluie tape la vitre du salon. Ça sent la soupe, tout bas. Le tapis rouge est un peu rêche. Un radiateur chauffe près du mur. Les cubes de bois sont dans une boîte. La boîte sent le sapin. Nino, tu vois les cubes ? Oui, papa. Je veux une tour. Papa pose déjà un cube bleu. Le cube jaune est encore dans sa main. En ce moment, Nino se penche. Le rouge, en haut. J'ai pas encore posé le jaune. Nino pose le rouge trop vite. La tour penche. Elle tombe. Les cubes roulent sous le canapé. Oh. Elle est par terre. La tour s'est arrêtée. On attend un peu ? Nino s'arrête à genoux. Le tapis gratte un peu. La pluie tape encore, plus fort. Je les cherche ? Oui. Sous le canapé, tout doux. Nino allonge le bras. Le dessous est frais, un peu sombre. Il touche un cube, puis l'autre. Le bleu. Le jaune. On les remet, un par un. Papa pose le bleu, bien à plat. Tu attends que je sois prêt ? Oui. On attend un peu. Nino tient le cube rouge. Le bois est lisse, un peu chaud. La soupe sent encore, plus près. La vitre est toute piquée de gouttes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le tapis bleu sent la laine un peu. Il est épais sous les genoux. Un cube rouge a roulé sous la table. Une caisse en bois dépasse du canapé. Dedans, des cubes rouges, jaunes, verts. Un rayon se pose sur un cube bleu. Le bois de la caisse est un peu rêche. Un coussin a glissé près de la caisse. La vapeur de soupe fait un petit nuage. La soupe sent bon, depuis la cuisine. Un fil de laine dépasse du tapis. Le canapé a un coussin un peu plat. Tu as vu le cube bleu, Aniss ? Oui, papa. Il brille. En ce moment, papa pose la caisse. Les cubes font un petit bruit de bois. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Aniss attend, un cube jaune dans la main. Puis il pose le cube. Le bois fait clic sur le tapis. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Aniss. On attend. Puis on pose un cube. Oui. Une règle simple. Je la rappelle une fois. Aniss attend encore. Puis il pose un cube rouge. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. La soupe sent encore, tout près. Le rayon a bougé sur le tapis. Encore un cube, tout doux ? Oui, papa. Aniss attend. Puis il pose un cube vert. Bravo. Tu as attendu. J'ai suivi la règle. Oui. Une règle. On la rappelle. Le coussin reste près de la caisse. Tu as les genoux sur le tapis ? Oui. Il est épais. On attend, puis on pose. Bravo. Aniss prend le cube sous la table. Il le pose dans la caisse, tout doux. Tu as suivi la règle. Une règle. On la rappelle. Puis on pose.</t>
+          <t>La pluie tape la vitre du salon. Ça sent la soupe, tout bas. Le tapis rouge est un peu rêche. Un radiateur chauffe près du mur. Les cubes de bois sont dans une boîte. La boîte sent le sapin. Nino, tu vois les cubes ? Oui, papa. Je veux une tour. Papa pose déjà un cube bleu. Le cube jaune est encore dans sa main. En ce moment, Nino se penche. Le rouge, en haut. J'ai pas encore posé le jaune. Nino pose le rouge trop vite. La tour penche. Elle tombe. Les cubes roulent sous le canapé. Oh. Elle est par terre. La tour s'est arrêtée. On attend un peu ? Nino s'arrête à genoux. Le tapis gratte un peu. La pluie tape encore, plus fort. Je les cherche ? Oui. Sous le canapé, tout doux. Nino allonge le bras. Le dessous est frais, un peu sombre. Il touche un cube, puis l'autre. Le bleu. Le jaune. On les remet, un par un. Papa pose le bleu, bien à plat. Tu attends que je sois prêt ? Oui. On attend un peu. Nino tient le cube rouge. Le bois est lisse, un peu chaud. La soupe sent encore, plus près. La vitre est toute piquée de gouttes.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,58 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le tapis bleu sent la laine un peu.
-narrateur|Il est épais sous les genoux.
-narrateur|Un cube rouge a roulé sous la table.
-narrateur|Une caisse en bois dépasse du canapé.
-narrateur|Dedans, des cubes rouges, jaunes, verts.
-narrateur|Un rayon se pose sur un cube bleu.
-narrateur|Le bois de la caisse est un peu rêche.
-narrateur|Un coussin a glissé près de la caisse.
-narrateur|La vapeur de soupe fait un petit nuage.
-narrateur|La soupe sent bon, depuis la cuisine.
-narrateur|Un fil de laine dépasse du tapis.
-narrateur|Le canapé a un coussin un peu plat.
-papa|Tu as vu le cube bleu, Aniss ?
-enfant-m|Oui, papa. Il brille.
-narrateur|En ce moment, papa pose la caisse.
-narrateur|Les cubes font un petit bruit de bois.
-papa|Une règle. On attend.
-papa|Puis on pose un cube.
-enfant-m|J'ai envie de poser.
-papa|On attend. Je te la rappelle une fois.
-papa|C'est la règle.
-narrateur|Aniss attend, un cube jaune dans la main.
-narrateur|Puis il pose le cube.
-narrateur|Le bois fait clic sur le tapis.
-enfant-m|Clic.
-papa|Tu as suivi la règle.
-papa|Tu as attendu. Bravo, Aniss.
-enfant-m|On attend. Puis on pose un cube.
-papa|Oui. Une règle simple.
-papa|Je la rappelle une fois.
-narrateur|Aniss attend encore.
-narrateur|Puis il pose un cube rouge.
-papa|Tu as suivi la règle dite.
-enfant-m|Une règle. On attend.
-papa|Oui. On la rappelle. Tu la suis.
-narrateur|La soupe sent encore, tout près.
-narrateur|Le rayon a bougé sur le tapis.
-papa|Encore un cube, tout doux ?
+          <t>narrateur|La pluie tape la vitre du salon.
+narrateur|Ça sent la soupe, tout bas.
+narrateur|Le tapis rouge est un peu rêche.
+narrateur|Un radiateur chauffe près du mur.
+narrateur|Les cubes de bois sont dans une boîte.
+narrateur|La boîte sent le sapin.
+papa|Nino, tu vois les cubes ?
 enfant-m|Oui, papa.
-narrateur|Aniss attend.
-narrateur|Puis il pose un cube vert.
-papa|Bravo. Tu as attendu.
-enfant-m|J'ai suivi la règle.
-papa|Oui. Une règle. On la rappelle.
-narrateur|Le coussin reste près de la caisse.
-papa|Tu as les genoux sur le tapis ?
-enfant-m|Oui. Il est épais.
-papa|On attend, puis on pose. Bravo.
-narrateur|Aniss prend le cube sous la table.
-narrateur|Il le pose dans la caisse, tout doux.
-papa|Tu as suivi la règle. Une règle.
-enfant-m|On la rappelle. Puis on pose.</t>
+enfant-m|Je veux une tour.
+narrateur|Papa pose déjà un cube bleu.
+narrateur|Le cube jaune est encore dans sa main.
+narrateur|En ce moment, Nino se penche.
+enfant-m|Le rouge, en haut.
+papa|J'ai pas encore posé le jaune.
+narrateur|Nino pose le rouge trop vite.
+narrateur|La tour penche.
+narrateur|Elle tombe.
+narrateur|Les cubes roulent sous le canapé.
+enfant-m|Oh.
+enfant-m|Elle est par terre.
+papa|La tour s'est arrêtée.
+papa|On attend un peu ?
+narrateur|Nino s'arrête à genoux.
+narrateur|Le tapis gratte un peu.
+narrateur|La pluie tape encore, plus fort.
+enfant-m|Je les cherche ?
+papa|Oui.
+papa|Sous le canapé, tout doux.
+narrateur|Nino allonge le bras.
+narrateur|Le dessous est frais, un peu sombre.
+narrateur|Il touche un cube, puis l'autre.
+enfant-m|Le bleu.
+enfant-m|Le jaune.
+papa|On les remet, un par un.
+narrateur|Papa pose le bleu, bien à plat.
+papa|Tu attends que je sois prêt ?
+enfant-m|Oui.
+papa|On attend un peu.
+narrateur|Nino tient le cube rouge.
+narrateur|Le bois est lisse, un peu chaud.
+narrateur|La soupe sent encore, plus près.
+narrateur|La vitre est toute piquée de gouttes.</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1392,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Aniss joue. Que suit-il ?</t>
+          <t>Nino veut la tour. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Aniss joue. Que suit-il ?</t>
+          <t>Nino veut la tour. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1417,12 +1407,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la règle</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la règle | une règle | attendre</t>
+          <t>attendre | on attend | un peu | son tour | elle attend | il attend | attendre un peu | on attend un peu | à son tour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1437,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Papa rappelle. Quelle chose Léandre suit ?</t>
+          <t>Il reste un peu. Que fait Nino d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1486,7 +1476,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1558,8 +1548,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Aniss joue.
-narrateur|Que suit-il ?</t>
+          <t>narrateur|Nino veut la tour.
+narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1576,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a suivi la règle. Papa l'a rappelée. Tu as attendu, puis tu as posé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le cube bleu brille encore un peu.</t>
+          <t>Nino reste encore un peu. Le bleu est à plat. Tu peux poser le jaune. Le jaune. Il pose tout doux. La tour ne penche pas. Maintenant le rouge ? Le rouge, en haut. Nino attend que papa lâche. Puis il pose. La tour tient, toute droite. Elle est haute ! Oui. Comme le fauteuil, presque. Un cube vert reste dans la boîte. Encore un ? Le vert. On attend un peu. Papa tient la base. Nino compte, sans poser. Maintenant. Le vert se pose, tout léger. Merci, Nino. Elle ne tombe plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a suivi la règle. Papa l'a rappelée. Tu as attendu, puis tu as posé ? Oui. Une règle. Bravo. On la rappelle, et on la suit. Le cube bleu brille encore un peu.</t>
+          <t>Nino reste encore un peu. Le bleu est à plat. Tu peux poser le jaune. Le jaune. Il pose tout doux. La tour ne penche pas. Maintenant le rouge ? Le rouge, en haut. Nino attend que papa lâche. Puis il pose. La tour tient, toute droite. Elle est haute ! Oui. Comme le fauteuil, presque. Un cube vert reste dans la boîte. Encore un ? Le vert. On attend un peu. Papa tient la base. Nino compte, sans poser. Maintenant. Le vert se pose, tout léger. Merci, Nino. Elle ne tombe plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1654,7 +1644,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1730,12 +1720,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aniss a suivi la règle.
-narrateur|Papa l'a rappelée.
-papa|Tu as attendu, puis tu as posé ?
-enfant-m|Oui. Une règle.
-papa|Bravo. On la rappelle, et on la suit.
-narrateur|Le cube bleu brille encore un peu.</t>
+          <t>narrateur|Nino reste encore un peu.
+papa|Le bleu est à plat.
+papa|Tu peux poser le jaune.
+enfant-m|Le jaune.
+narrateur|Il pose tout doux.
+narrateur|La tour ne penche pas.
+papa|Maintenant le rouge ?
+enfant-m|Le rouge, en haut.
+narrateur|Nino attend que papa lâche.
+narrateur|Puis il pose.
+narrateur|La tour tient, toute droite.
+enfant-m|Elle est haute !
+papa|Oui.
+papa|Comme le fauteuil, presque.
+narrateur|Un cube vert reste dans la boîte.
+papa|Encore un ?
+enfant-m|Le vert.
+papa|On attend un peu.
+narrateur|Papa tient la base.
+narrateur|Nino compte, sans poser.
+papa|Maintenant.
+narrateur|Le vert se pose, tout léger.
+papa|Merci, Nino.
+enfant-m|Elle ne tombe plus.</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1770,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range les cubes ? Oui, papa. Papa range les cubes dans la caisse. Aniss donne la main. On va vers la soupe ? Oui. Elle sent bon. Le tapis bleu reste un peu chaud. Le fil de laine, tu l'as vu ? Oui. Il dépasse. La vapeur de soupe est encore là.</t>
+          <t>On va voir la pluie ? Elle tape fort. Ils s'approchent de la vitre. Les gouttes glissent, l'une après l'autre. Comme les cubes. Une, puis l'autre. La tour reste au milieu du tapis. Le radiateur fait un petit bruit. On goûte la soupe ? Un peu. La cuillère est tiède. Ça sent la carotte. Elle est bonne. La tour attend encore. Je rajoute un cube ? Oui. Quand je tiens le bas. Ils reviennent au tapis. Nino attend, le cube orange en main. Tu es prêt ? Oui, papa. Il pose. La tour touche presque le fauteuil. Elle est grande. Oui. Un cube, puis l'autre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On range les cubes ? Oui, papa. Papa range les cubes dans la caisse. Aniss donne la main. On va vers la soupe ? Oui. Elle sent bon. Le tapis bleu reste un peu chaud. Le fil de laine, tu l'as vu ? Oui. Il dépasse. La vapeur de soupe est encore là.</t>
+          <t>On va voir la pluie ? Elle tape fort. Ils s'approchent de la vitre. Les gouttes glissent, l'une après l'autre. Comme les cubes. Une, puis l'autre. La tour reste au milieu du tapis. Le radiateur fait un petit bruit. On goûte la soupe ? Un peu. La cuillère est tiède. Ça sent la carotte. Elle est bonne. La tour attend encore. Je rajoute un cube ? Oui. Quand je tiens le bas. Ils reviennent au tapis. Nino attend, le cube orange en main. Tu es prêt ? Oui, papa. Il pose. La tour touche presque le fauteuil. Elle est grande. Oui. Un cube, puis l'autre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1830,7 +1838,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1902,16 +1910,32 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>papa|On range les cubes ?
+          <t>papa|On va voir la pluie ?
+enfant-m|Elle tape fort.
+narrateur|Ils s'approchent de la vitre.
+narrateur|Les gouttes glissent, l'une après l'autre.
+enfant-m|Comme les cubes.
+papa|Une, puis l'autre.
+narrateur|La tour reste au milieu du tapis.
+narrateur|Le radiateur fait un petit bruit.
+papa|On goûte la soupe ?
+enfant-m|Un peu.
+narrateur|La cuillère est tiède.
+narrateur|Ça sent la carotte.
+enfant-m|Elle est bonne.
+papa|La tour attend encore.
+enfant-m|Je rajoute un cube ?
+papa|Oui.
+papa|Quand je tiens le bas.
+narrateur|Ils reviennent au tapis.
+narrateur|Nino attend, le cube orange en main.
+papa|Tu es prêt ?
 enfant-m|Oui, papa.
-narrateur|Papa range les cubes dans la caisse.
-narrateur|Aniss donne la main.
-papa|On va vers la soupe ?
-enfant-m|Oui. Elle sent bon.
-narrateur|Le tapis bleu reste un peu chaud.
-papa|Le fil de laine, tu l'as vu ?
-enfant-m|Oui. Il dépasse.
-narrateur|La vapeur de soupe est encore là.</t>
+narrateur|Il pose.
+narrateur|La tour touche presque le fauteuil.
+enfant-m|Elle est grande.
+papa|Oui.
+papa|Un cube, puis l'autre.</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1962,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La soupe fume dans les bols. J'ai attendu. Puis j'ai posé. Oui. Tu as suivi la règle. Bravo, Aniss.</t>
+          <t>La tour est plus haute que moi. Et toi, tu as attendu. Bravo, Nino. La pluie tape encore la vitre. Le bois de la tour sent le sapin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La soupe fume dans les bols. J'ai attendu. Puis j'ai posé. Oui. Tu as suivi la règle. Bravo, Aniss.</t>
+          <t>La tour est plus haute que moi. Et toi, tu as attendu. Bravo, Nino. La pluie tape encore la vitre. Le bois de la tour sent le sapin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1999,14 +2023,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2078,10 +2102,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|La soupe fume dans les bols.
-enfant-m|J'ai attendu. Puis j'ai posé.
-papa|Oui. Tu as suivi la règle.
-papa|Bravo, Aniss.</t>
+          <t>enfant-m|La tour est plus haute que moi.
+papa|Et toi, tu as attendu.
+papa|Bravo, Nino.
+narrateur|La pluie tape encore la vitre.
+narrateur|Le bois de la tour sent le sapin.</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2177,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
